--- a/docs/Glimmora_Go_Spec.xlsx
+++ b/docs/Glimmora_Go_Spec.xlsx
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -205,9 +205,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1834,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2632,12 +2629,12 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Document file upload</t>
+          <t>Document file upload UI</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Actually uploading files to storage</t>
+          <t>Pick type + file, POST /api/uploads/driver-doc, stored under public/uploads/drivers/</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2645,16 +2642,12 @@
           <t>SUPER/ADMIN/CITY/VERIF</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>fileUrl field exists but no upload UI</t>
-        </is>
-      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -2701,175 +2694,181 @@
       <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Riders JSON API</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>GET /api/riders (q/limit/offset), GET /api/riders/[id] with rides + stats</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>riders:read</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>For external clients and future rider app</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>FARES</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>/fares</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Per-city fare editor</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Base fare, per km, per min, minimum fare</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN/CITY (write) · VIEW (read)</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>CITY sees own city only</t>
-        </is>
-      </c>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>/fares</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Per-city fare editor</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Base fare, per km, per min, minimum fare</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY (write) · VIEW (read)</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CITY sees own city only</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>/fares</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Saved ✓ feedback</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>2s confirmation after PUT</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>CONCESSIONS</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>/concessions</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Per-city multipliers</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Women, senior, children — default 0.85/0.80/0.90</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>SUPER/ADMIN (write) · VIEW (read)</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>COUPONS</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="15" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>/coupons</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Create coupon</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Code, description, FLAT/PERCENT, amount, usage limit, expiry</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
@@ -2878,17 +2877,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>List + usage stats</t>
+          <t>Create coupon</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Used count / limit, expiry date, active/disabled/expired badge</t>
+          <t>Code, description, FLAT/PERCENT, amount, usage limit, expiry</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>same + VIEW read</t>
+          <t>SUPER/ADMIN</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -2900,86 +2899,82 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>/coupons</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>List + usage stats</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Used count / limit, expiry date, active/disabled/expired badge</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>same + VIEW read</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>/coupons</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Disable / Enable / Delete</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>PATCH active flag / DELETE</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>SUPER/ADMIN</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>CITIES</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="15" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>/cities</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Archetype defaults editor</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Per-archetype (Metro/Small Town) defaults: radius, surge, payment options, base, perKm, perMin, minFare</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN (write) · VIEW (read)</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>New cities inherit these</t>
-        </is>
-      </c>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -2988,17 +2983,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Add city form</t>
+          <t>Archetype defaults editor</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Name + state + archetype</t>
+          <t>Per-archetype (Metro/Small Town) defaults: radius, surge, payment options, base, perKm, perMin, minFare</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>SUPER/ADMIN</t>
+          <t>SUPER/ADMIN (write) · VIEW (read)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -3006,86 +3001,90 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>New cities inherit these</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>/cities</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Add city form</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Name + state + archetype</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>/cities</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Per-city edit row</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Archetype override, matching radius, surge, active toggle, payment pills</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>SUPER/ADMIN</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>REFERRALS</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n"/>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="14" t="n"/>
-      <c r="G44" s="15" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>/referrals</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Stat cards</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Total / joined / rewarded with conversion %</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN (write) · VIEW (read)</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
@@ -3094,17 +3093,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Top referrers list</t>
+          <t>Stat cards</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Top 5 drivers by referredDrivers count</t>
+          <t>Total / joined / rewarded with conversion %</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>SUPER/ADMIN (write) · VIEW (read)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -3116,7 +3115,7 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
@@ -3125,12 +3124,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Recent referrals table</t>
+          <t>Top referrers list</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Referee phone, rides done / 10, status (Pending/Joined/Rewarded), date</t>
+          <t>Top 5 drivers by referredDrivers count</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3147,7 +3146,7 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
@@ -3156,17 +3155,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Issue / Revoke reward</t>
+          <t>Recent referrals table</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Manual toggle on Referral.rewardIssued</t>
+          <t>Referee phone, rides done / 10, status (Pending/Joined/Rewarded), date</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>SUPER/ADMIN</t>
+          <t>same</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -3178,7 +3177,7 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
@@ -3187,12 +3186,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Mark joined</t>
+          <t>Issue / Revoke reward</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Manual toggle on refereeJoined</t>
+          <t>Manual toggle on Referral.rewardIssued</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -3209,7 +3208,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
@@ -3218,12 +3217,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Recompute rewards button</t>
+          <t>Mark joined</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Scans all drivers, grants rewards for any who crossed 10 rides</t>
+          <t>Manual toggle on refereeJoined</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -3240,82 +3239,82 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>/referrals</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Recompute rewards button</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Scans all drivers, grants rewards for any who crossed 10 rides</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>automation</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Auto-reward on ride complete</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>On PATCH action=COMPLETE, if driver was referred + hit 10 rides, extend referrer subscriptionUntil by 7 days</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>REPORTS</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n"/>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="15" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>/reports</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Range pills</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Last 7 / 14 / 30 / 90 days</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN/CITY/SUPP/VIEW</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
+      <c r="B53" s="14" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
+      <c r="E53" s="14" t="n"/>
+      <c r="F53" s="14" t="n"/>
+      <c r="G53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
@@ -3324,17 +3323,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Stat cards</t>
+          <t>Range pills</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Rides, revenue, completion %, active drivers</t>
+          <t>Last 7 / 14 / 30 / 90 days</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>SUPER/ADMIN/CITY/SUPP/VIEW</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -3346,7 +3345,7 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
@@ -3355,12 +3354,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Stat cards</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Rides-per-day bar, revenue line, booking-channel donut</t>
+          <t>Rides, revenue, completion %, active drivers</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -3373,15 +3372,11 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Chart.js</t>
-        </is>
-      </c>
+      <c r="G55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
@@ -3390,12 +3385,12 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>By-city breakdown</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Rides, completion %, revenue per city</t>
+          <t>Rides-per-day bar, revenue line, booking-channel donut</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3408,11 +3403,15 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Chart.js</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
@@ -3421,12 +3420,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Top drivers table</t>
+          <t>By-city breakdown</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Top 10 by rides + revenue</t>
+          <t>Rides, completion %, revenue per city</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -3443,86 +3442,86 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>/reports</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Top drivers table</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Top 10 by rides + revenue</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>/reports</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>CSV export</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>GET /api/reports/export?days=N → rides-Nd-YYYY-MM-DD.csv</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>City-filtered for CITY_ADMIN</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>KIRANA PARTNERS (admin side)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="n"/>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="15" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>/partners</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Partner list with status filter</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Shop, owner, phone, city, commission %, bookings count, status + review note</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN/CITY (write) · VIEW (read)</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="14" t="n"/>
+      <c r="G60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
@@ -3531,17 +3530,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Approve / Reject / Suspend</t>
+          <t>Partner list with status filter</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>PATCH status + optional reviewNote</t>
+          <t>Shop, owner, phone, city, commission %, bookings count, status + review note</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>SUPER/ADMIN/CITY</t>
+          <t>SUPER/ADMIN/CITY (write) · VIEW (read)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -3553,211 +3552,213 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>/partners</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Approve / Reject / Suspend</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>PATCH status + optional reviewNote</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>/partners</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Commission % editor</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Per-partner override (default 10%)</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>SUBSCRIPTIONS</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n"/>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" s="14" t="n"/>
+      <c r="E64" s="14" t="n"/>
+      <c r="F64" s="14" t="n"/>
+      <c r="G64" s="15" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>/subscriptions</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Subscription list + stats</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>All driver plans with active/expired/revoked status; active/total/revenue cards</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN (write) · VIEW (read)</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>/subscriptions</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Grant subscription</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Pick approved driver + plan (DAILY/WEEKLY/MONTHLY) + amount; stacks on existing expiry</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>/subscriptions</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Revoke / Reinstate</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>PATCH active flag; rolls back driver.subscriptionUntil if all plans inactive</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>ADMIN USER MGMT</t>
         </is>
       </c>
-      <c r="B63" s="14" t="n"/>
-      <c r="C63" s="14" t="n"/>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="14" t="n"/>
-      <c r="G63" s="15" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>/admins</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Create admin form</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Email, name, password (8+), role, city picker (if CITY_ADMIN)</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Super Admin only</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>/admins</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Admin list</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Name, email, role badge, city, active/disabled, joined</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Super Admin only to see controls</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Non-super sees list read-only</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>/admins</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Enable / Disable / Delete</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Self-delete + self-deactivate blocked</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Super Admin only</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>CROSS-CUTTING</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="n"/>
-      <c r="C67" s="14" t="n"/>
-      <c r="D67" s="14" t="n"/>
-      <c r="E67" s="14" t="n"/>
-      <c r="F67" s="14" t="n"/>
-      <c r="G67" s="15" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>sidebar</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Role-filtered nav</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Hide pages user can't access; role label under logo</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="14" t="n"/>
+      <c r="F68" s="14" t="n"/>
+      <c r="G68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>layout</t>
+          <t>/admins</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Session enforcement</t>
+          <t>Create admin form</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>requireAccess(surface) on every page; redirects unauthorized to /</t>
+          <t>Email, name, password (8+), role, city picker (if CITY_ADMIN)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>Super Admin only</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -3769,26 +3770,26 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>/admins</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>requireWrite + cityMismatch</t>
+          <t>Admin list</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Centralized guards on every API mutation</t>
+          <t>Name, email, role badge, city, active/disabled, joined</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>Super Admin only to see controls</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -3796,165 +3797,307 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Non-super sees list read-only</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>/admins</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>i18n Hindi + English toggle</t>
+          <t>Enable / Disable / Delete</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>next-intl across all admin strings</t>
+          <t>Self-delete + self-deactivate blocked</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Tracker #20, Low priority</t>
-        </is>
-      </c>
+          <t>Super Admin only</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Audit log / compliance module</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Track who changed what, when</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>SUPER/ADMIN</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Post-MVP per SOW</t>
-        </is>
-      </c>
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>CROSS-CUTTING</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>sidebar</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Enterprise admin console</t>
+          <t>Role-filtered nav</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Corporate/fleet accounts</t>
+          <t>Hide pages user can't access; role label under logo</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Post-MVP</t>
-        </is>
-      </c>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Session enforcement</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>requireAccess(surface) on every page; redirects unauthorized to /</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>requireWrite + cityMismatch</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Centralized guards on every API mutation</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>i18n Hindi + English toggle</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>next-intl across all admin strings</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Tracker #20, Low priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Audit log / compliance module</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Track who changed what, when</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN</t>
+        </is>
+      </c>
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Post-MVP per SOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise admin console</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Corporate/fleet accounts</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Post-MVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>global</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>Socket.io realtime rides</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Replace polling with live push</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
+      <c r="F79" s="16" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Backend dependency</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A44:G44"/>
+  <mergeCells count="16">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A68:G68"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3966,7 +4109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4470,12 +4613,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Map-based pickup picker</t>
+          <t>Map-based pickup/drop picker</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Click map / search to set pickup</t>
+          <t>Leaflet + OSM Nominatim; click map or search address to set pickup and drop</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -4483,16 +4626,12 @@
           <t>same</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Requires Google Places or OSM Nominatim</t>
-        </is>
-      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -4829,12 +4968,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>KYC document upload</t>
+          <t>KYC document upload + status</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Shop license, aadhaar, etc.</t>
+          <t>Pick type + file, upload to /api/kirana/documents; shows per-doc PENDING/APPROVED/REJECTED badge</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -4842,16 +4981,12 @@
           <t>same</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>PartnerDocument model exists, no upload UI</t>
-        </is>
-      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4931,7 +5066,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>CROSS-CUTTING</t>
+          <t>PWA SHELL</t>
         </is>
       </c>
       <c r="B33" s="14" t="n"/>
@@ -4942,206 +5077,366 @@
       <c r="G33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>manifest</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Web App Manifest</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>public/manifest.webmanifest scoped to /k/ with name/icons/theme/start_url</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>icons</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>App icons + apple-touch</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>192/512 PNG + maskable 512 + 180 apple-touch, brand orange 'GG' monogram</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Generated via scripts/build-pwa-icons.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>service-worker</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Service worker (/sw.js, scope /k/)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Cache-first static, network-first kirana APIs, offline fallback to /offline.html</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Service-Worker-Allowed header set in next.config.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Install prompt component</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Captures beforeinstallprompt, shows 'Add to home screen' banner with dismiss persistence</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Approved partner</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Push notifications</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Driver matched / arrived / completed alerts</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>SW ready; needs VAPID + backend trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>CROSS-CUTTING</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>OTP</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>6-digit, 5-min TTL</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>OtpRequest table; single-use (usedAt timestamp)</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>OTP</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>MSG91 send</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Actually send the code via SMS</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Stubbed; returns devCode in dev</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
+    <row r="42">
+      <c r="A42" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>fare</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Haversine + concession</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>src/lib/fare.ts shared with future rider/driver apps</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>commission</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Payout / settlement</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Actually paying partners their earned commission</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Tracks earned; no payout flow</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Booking status notifications</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Driver matched / arrived / completed alerts</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Hindi + English toggle</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>react-i18next across all kirana strings</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>i18n</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Hindi + English toggle</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>react-i18next across all kirana strings</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Low priority</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
@@ -5157,7 +5452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5413,7 +5708,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -5423,12 +5718,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Approve/reject driver doc + review note</t>
+          <t>Fetch single driver document</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>documents:write + city scope</t>
+          <t>documents:read + city scope</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -5445,17 +5740,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>/api/rides/[id]</t>
+          <t>/api/drivers/[id]/documents/[docId]</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Cancel / Complete / Reassign driver</t>
+          <t>Approve/reject driver doc + review note</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>rides:write + city scope</t>
+          <t>documents:write + city scope</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -5467,22 +5762,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>/api/rides/[id]/token</t>
+          <t>/api/drivers/[id]/documents/[docId]</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Generate or fetch public tracking token</t>
+          <t>Delete driver doc + file</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>rides:write + city scope</t>
+          <t>documents:write + city scope</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -5499,17 +5794,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>/api/coupons</t>
+          <t>/api/uploads/driver-doc</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Create coupon</t>
+          <t>Upload driver doc file to storage</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>coupons:write</t>
+          <t>documents:write + city scope</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -5521,22 +5816,22 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>/api/coupons/[id]</t>
+          <t>/api/riders</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Toggle active</t>
+          <t>List riders (q/limit/offset)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>coupons:write</t>
+          <t>riders:read</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -5548,22 +5843,22 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>/api/coupons/[id]</t>
+          <t>/api/riders/[id]</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Delete coupon</t>
+          <t>Rider detail with recent rides + stats</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>coupons:write</t>
+          <t>riders:read</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -5575,22 +5870,22 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>/api/referrals/[id]</t>
+          <t>/api/subscriptions</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Manual reward issue/revoke</t>
+          <t>List subscriptions (optional driverId/active filters)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>referrals:write</t>
+          <t>subscriptions:read</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -5607,17 +5902,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>/api/referrals/recompute</t>
+          <t>/api/subscriptions</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Recompute all pending referral rewards</t>
+          <t>Grant subscription (stacks on existing expiry)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>referrals:write</t>
+          <t>subscriptions:write</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -5629,22 +5924,22 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>/api/reports/export</t>
+          <t>/api/subscriptions/[id]</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>CSV download, city-filtered</t>
+          <t>Revoke / reinstate subscription</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>reports:read</t>
+          <t>subscriptions:write</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -5656,22 +5951,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>/api/sos</t>
+          <t>/api/rides/[id]</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Active SOS count (sidebar badge)</t>
+          <t>Cancel / Complete / Reassign driver</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>sos:read + city filter</t>
+          <t>rides:write + city scope</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -5688,17 +5983,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>/api/admins</t>
+          <t>/api/rides/[id]/token</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Create admin user</t>
+          <t>Generate or fetch public tracking token</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>rides:write + city scope</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -5710,22 +6005,22 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>/api/admins/[id]</t>
+          <t>/api/coupons</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Enable/disable, change role/city/password</t>
+          <t>Create coupon</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>coupons:write</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -5737,22 +6032,22 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>/api/admins/[id]</t>
+          <t>/api/coupons/[id]</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Delete admin</t>
+          <t>Toggle active</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>coupons:write</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -5764,22 +6059,22 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>/api/partners/[id]</t>
+          <t>/api/coupons/[id]</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Approve/reject/suspend + commission %</t>
+          <t>Delete coupon</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>partners:write + city scope</t>
+          <t>coupons:write</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -5791,22 +6086,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>/api/track/[token]</t>
+          <t>/api/referrals/[id]</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Public ride state for tracking page</t>
+          <t>Manual reward issue/revoke</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>referrals:write</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -5823,17 +6118,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/signup</t>
+          <t>/api/referrals/recompute</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Partner application (creates PENDING)</t>
+          <t>Recompute all pending referral rewards</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>referrals:write</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -5845,22 +6140,22 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/request</t>
+          <t>/api/reports/export</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Generate 6-digit OTP (phone must belong to a partner)</t>
+          <t>CSV download, city-filtered</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>reports:read</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -5872,22 +6167,22 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/verify</t>
+          <t>/api/sos</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Verify OTP + set kirana session cookie</t>
+          <t>Active SOS count (sidebar badge)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>sos:read + city filter</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -5904,17 +6199,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/logout</t>
+          <t>/api/admins</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Clear kirana session</t>
+          <t>Create admin user</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>kirana session</t>
+          <t>SUPER_ADMIN</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -5926,22 +6221,22 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/bookings</t>
+          <t>/api/admins/[id]</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Fare estimate without creating</t>
+          <t>Enable/disable, change role/city/password</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>kirana session (any status)</t>
+          <t>SUPER_ADMIN</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -5953,25 +6248,241 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>/api/admins/[id]</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Delete admin</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>/api/partners/[id]</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Approve/reject/suspend + commission %</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>partners:write + city scope</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>/api/track/[token]</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Public ride state for tracking page</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/signup</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Partner application (creates PENDING)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/otp/request</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Generate 6-digit OTP (phone must belong to a partner)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/otp/verify</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Verify OTP + set kirana session cookie</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/logout</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Clear kirana session</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>kirana session</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>/api/kirana/bookings</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Fare estimate without creating</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>kirana session (any status)</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/bookings</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Create booking (REQUESTED ride with bookedByPartnerId)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>kirana session (APPROVED only)</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6178,12 +6689,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>driver detail</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Done (no upload UI)</t>
+          <t>driver detail + upload UI</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6556,12 +7067,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Referral reward extends this</t>
+          <t>/subscriptions admin + referral reward extends this</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Schema only (no purchase UI)</t>
+          <t>Done (admin grant; no driver-side purchase UI)</t>
         </is>
       </c>
     </row>
@@ -6660,12 +7171,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Schema only (no UI)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>Kirana /k/profile upload + /partners/[id] review</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -6734,7 +7245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7376,12 +7887,12 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Need Vercel Blob or S3</t>
+          <t>Shipped — stored under public/uploads/ in dev; production should swap to Vercel Blob / S3</t>
         </is>
       </c>
     </row>
@@ -7586,12 +8097,12 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Google Places or Nominatim</t>
+          <t>Shipped — Leaflet + Nominatim</t>
         </is>
       </c>
     </row>
@@ -7629,6 +8140,142 @@
           <t>SOW explicitly deferred to Phase 2</t>
         </is>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Driver subscription purchase UI</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Driver PWA</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>App Dev + Backend</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Drivers buying their own plan; admin grant exists</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Admin /subscriptions shipped; waits on payments + Driver app</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>VAPID push notifications</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>RN/PWA + Backend</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>App Dev + Backend</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Booking status push to kirana partners</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>PWA service worker ready; needs backend trigger + VAPID keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Bookings detail + live track in Kirana PWA</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Kirana PWA</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Partner can't watch a ride they booked</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Token API + public /track page already exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Per-document DELETE in partner docs review</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Admins can approve/reject but not remove partner docs</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/Glimmora_Go_Spec.xlsx
+++ b/docs/Glimmora_Go_Spec.xlsx
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,9 +202,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -957,7 +954,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Admin Panel (read-only + complaints)</t>
+          <t>Admin Panel (read + tickets write)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -967,17 +964,17 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Monitor live rides, riders, reports, SOS alerts. (Ticketing module TODO.)</t>
+          <t>Monitor live rides, riders, reports, SOS; triage and resolve support tickets</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Read-only global</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Done (no tickets module yet)</t>
+          <t>Read-only global; write on tickets</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1739,82 +1736,208 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Track public</t>
+          <t>Tickets</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>W (own city)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Public, opaque token</t>
+          <t>SUPPORT role can triage</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>Audit / Compliance</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Read-only log; fraud signals panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise (B2B)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>W (own city)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Corporate accounts + wallet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Track public</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Public, opaque token</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>Kirana PWA</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Separate auth; agents only</t>
         </is>
@@ -1831,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3727,7 +3850,7 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>ADMIN USER MGMT</t>
+          <t>TICKETS / COMPLAINTS</t>
         </is>
       </c>
       <c r="B68" s="14" t="n"/>
@@ -3738,27 +3861,29 @@
       <c r="G68" s="15" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n">
-        <v>48</v>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>/admins</t>
+          <t>/tickets</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Create admin form</t>
+          <t>Tickets list + counters</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Email, name, password (8+), role, city picker (if CITY_ADMIN)</t>
+          <t>Open / In-progress / Total cards; status filter pills; city-scoped for CITY_ADMIN</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Super Admin only</t>
+          <t>SUPER/ADMIN/CITY/SUPPORT (write) · VIEW (read)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -3769,27 +3894,29 @@
       <c r="G69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="n">
-        <v>49</v>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>/admins</t>
+          <t>/tickets</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Admin list</t>
+          <t>Create ticket</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Name, email, role badge, city, active/disabled, joined</t>
+          <t>Subject, category, priority, description, optional rider/ride links</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Super Admin only to see controls</t>
+          <t>SUPER/ADMIN/CITY/SUPPORT</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -3797,34 +3924,32 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Non-super sees list read-only</t>
-        </is>
-      </c>
+      <c r="G70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n">
-        <v>50</v>
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>/admins</t>
+          <t>/tickets/[id]</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Enable / Disable / Delete</t>
+          <t>Ticket detail + triage</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Self-delete + self-deactivate blocked</t>
+          <t>Status + priority + assignee + resolution note; linked rider/driver/ride</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Super Admin only</t>
+          <t>SUPER/ADMIN/CITY/SUPPORT</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -3837,7 +3962,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>CROSS-CUTTING</t>
+          <t>AUDIT &amp; COMPLIANCE</t>
         </is>
       </c>
       <c r="B72" s="14" t="n"/>
@@ -3848,256 +3973,700 @@
       <c r="G72" s="15" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="n">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>/audit</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Audit event log</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Filter by entity / admin / range (24h/7d/30d/90d); shows who + what + summary + IP</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/VIEW (read)</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Hooked into drivers/coupons/partners/admins/subscriptions/tickets/corporates APIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>/audit</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Fraud &amp; compliance signals</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Stale PENDING drivers, doc rejection repeats, unresolved SOS &gt;24h, duplicate rider accounts, high-cancellation drivers</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>/api/audit/export</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>CSV export</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Download audit events over N-day range</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>ENTERPRISE (CORPORATES)</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n"/>
+      <c r="C76" s="14" t="n"/>
+      <c r="D76" s="14" t="n"/>
+      <c r="E76" s="14" t="n"/>
+      <c r="F76" s="14" t="n"/>
+      <c r="G76" s="15" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>/corporates</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Corporate accounts list</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Name, contact, city, members/rides count, wallet, status</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY (write) · VIEW (read)</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>/corporates</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Create corporate account</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Name, GSTIN, contact (name/email/phone), city</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>/corporates/[id]</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Corporate detail</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Status + wallet + members + recent rides + wallet history</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>/corporates/[id]</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Approve / Suspend / Review note</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>PATCH status + reviewNote</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>/corporates/[id]</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Members management</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Add rider by phone (auto-creates rider), set employee ID, remove</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>/corporates/[id]</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Wallet top-up / debit</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Manual ledger entries with note; affects walletBalance transactionally</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>SUPER/ADMIN/CITY</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Ride-fare deduction not wired yet — depends on payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN USER MGMT</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="n"/>
+      <c r="C83" s="14" t="n"/>
+      <c r="D83" s="14" t="n"/>
+      <c r="E83" s="14" t="n"/>
+      <c r="F83" s="14" t="n"/>
+      <c r="G83" s="15" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>/admins</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Create admin form</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Email, name, password (8+), role, city picker (if CITY_ADMIN)</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Super Admin only</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>/admins</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Admin list</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Name, email, role badge, city, active/disabled, joined</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Super Admin only to see controls</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Non-super sees list read-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>/admins</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Enable / Disable / Delete</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Self-delete + self-deactivate blocked</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Super Admin only</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>CROSS-CUTTING</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="n"/>
+      <c r="C87" s="14" t="n"/>
+      <c r="D87" s="14" t="n"/>
+      <c r="E87" s="14" t="n"/>
+      <c r="F87" s="14" t="n"/>
+      <c r="G87" s="15" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>sidebar</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>Role-filtered nav</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>Hide pages user can't access; role label under logo</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="n">
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>layout</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>Session enforcement</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>requireAccess(surface) on every page; redirects unauthorized to /</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="n">
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>requireWrite + cityMismatch</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Centralized guards on every API mutation</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="n">
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>global</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>i18n Hindi + English toggle</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>next-intl across all admin strings</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="F76" s="16" t="inlineStr">
+      <c r="F91" s="16" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Tracker #20, Low priority</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="n">
+    <row r="92">
+      <c r="A92" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>global</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>Audit log / compliance module</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Track who changed what, when</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Track who changed what, when + fraud signals</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>SUPER/ADMIN</t>
         </is>
       </c>
-      <c r="F77" s="16" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Shipped in /audit + /api/audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise admin console</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Corporate/fleet accounts with wallet + members</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Shipped in /corporates; ride-fare deduction waits on payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Socket.io realtime rides</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Replace polling with live push</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Post-MVP per SOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Enterprise admin console</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Corporate/fleet accounts</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Post-MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Socket.io realtime rides</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Replace polling with live push</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="16" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Backend dependency</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="19">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A72:G72"/>
     <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A83:G83"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A87:G87"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A76:G76"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5452,7 +6021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5951,22 +6520,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>/api/rides/[id]</t>
+          <t>/api/tickets</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cancel / Complete / Reassign driver</t>
+          <t>List tickets (status/category/q filters, city-scoped)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>rides:write + city scope</t>
+          <t>tickets:read</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -5983,17 +6552,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>/api/rides/[id]/token</t>
+          <t>/api/tickets</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Generate or fetch public tracking token</t>
+          <t>Create ticket</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>rides:write + city scope</t>
+          <t>tickets:write</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -6005,22 +6574,22 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>/api/coupons</t>
+          <t>/api/tickets/[id]</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Create coupon</t>
+          <t>Update status/priority/assignee/resolution</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>coupons:write</t>
+          <t>tickets:write + city scope</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -6032,22 +6601,22 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>/api/coupons/[id]</t>
+          <t>/api/audit</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Toggle active</t>
+          <t>List audit events (entityType/admin/since filters)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>coupons:write</t>
+          <t>audit:read</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -6059,22 +6628,22 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>/api/coupons/[id]</t>
+          <t>/api/audit/export</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Delete coupon</t>
+          <t>CSV export of audit events</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>coupons:write</t>
+          <t>audit:read</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -6086,22 +6655,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>/api/referrals/[id]</t>
+          <t>/api/corporates</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Manual reward issue/revoke</t>
+          <t>List corporates (status filter, city-scoped)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>referrals:write</t>
+          <t>corporates:read</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -6118,17 +6687,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>/api/referrals/recompute</t>
+          <t>/api/corporates</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Recompute all pending referral rewards</t>
+          <t>Create corporate account</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>referrals:write</t>
+          <t>corporates:write</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -6140,22 +6709,22 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>/api/reports/export</t>
+          <t>/api/corporates/[id]</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>CSV download, city-filtered</t>
+          <t>Update status / review note / contact</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>reports:read</t>
+          <t>corporates:write + city scope</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -6167,22 +6736,22 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>/api/sos</t>
+          <t>/api/corporates/[id]/members</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Active SOS count (sidebar badge)</t>
+          <t>Add rider to corporate (auto-creates rider)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>sos:read + city filter</t>
+          <t>corporates:write</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -6194,22 +6763,22 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>/api/admins</t>
+          <t>/api/corporates/[id]/members/[memberId]</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Create admin user</t>
+          <t>Remove member</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>corporates:write</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -6221,22 +6790,22 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>/api/admins/[id]</t>
+          <t>/api/corporates/[id]/top-up</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Enable/disable, change role/city/password</t>
+          <t>Credit / debit corporate wallet (transactional)</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>corporates:write</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -6248,22 +6817,22 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>/api/admins/[id]</t>
+          <t>/api/rides/[id]</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Delete admin</t>
+          <t>Cancel / Complete / Reassign driver</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>SUPER_ADMIN</t>
+          <t>rides:write + city scope</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -6275,22 +6844,22 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>/api/partners/[id]</t>
+          <t>/api/rides/[id]/token</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Approve/reject/suspend + commission %</t>
+          <t>Generate or fetch public tracking token</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>partners:write + city scope</t>
+          <t>rides:write + city scope</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -6302,22 +6871,22 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>/api/track/[token]</t>
+          <t>/api/coupons</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Public ride state for tracking page</t>
+          <t>Create coupon</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>coupons:write</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -6329,22 +6898,22 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/signup</t>
+          <t>/api/coupons/[id]</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Partner application (creates PENDING)</t>
+          <t>Toggle active</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>coupons:write</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -6356,22 +6925,22 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/request</t>
+          <t>/api/coupons/[id]</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Generate 6-digit OTP (phone must belong to a partner)</t>
+          <t>Delete coupon</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>coupons:write</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -6383,22 +6952,22 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/verify</t>
+          <t>/api/referrals/[id]</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Verify OTP + set kirana session cookie</t>
+          <t>Manual reward issue/revoke</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>referrals:write</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -6415,17 +6984,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/logout</t>
+          <t>/api/referrals/recompute</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Clear kirana session</t>
+          <t>Recompute all pending referral rewards</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>kirana session</t>
+          <t>referrals:write</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -6437,22 +7006,22 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/bookings</t>
+          <t>/api/reports/export</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Fare estimate without creating</t>
+          <t>CSV download, city-filtered</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>kirana session (any status)</t>
+          <t>reports:read</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -6464,25 +7033,322 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>/api/sos</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Active SOS count (sidebar badge)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>sos:read + city filter</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>/api/admins</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Create admin user</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>/api/admins/[id]</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Enable/disable, change role/city/password</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>/api/admins/[id]</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Delete admin</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>/api/partners/[id]</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Approve/reject/suspend + commission %</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>partners:write + city scope</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>/api/track/[token]</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Public ride state for tracking page</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/signup</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Partner application (creates PENDING)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/otp/request</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Generate 6-digit OTP (phone must belong to a partner)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/otp/verify</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Verify OTP + set kirana session cookie</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/logout</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Clear kirana session</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>kirana session</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>/api/kirana/bookings</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Fare estimate without creating</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>kirana session (any status)</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>/api/kirana/bookings</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Create booking (REQUESTED ride with bookedByPartnerId)</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>kirana session (APPROVED only)</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -6499,7 +7365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7231,6 +8097,249 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Done (only Kirana used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Complaints / support tickets</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>category, priority, status, assignee, rider/driver/ride/city links, resolution</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>/tickets + /tickets/[id] + audit hook</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>TicketCategory</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Ticket category</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>RIDE_ISSUE, SAFETY, PAYMENT, DRIVER_BEHAVIOR, APP, OTHER</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ticket create form</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>TicketStatus</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Ticket lifecycle</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>OPEN, IN_PROGRESS, RESOLVED, CLOSED</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>/tickets pills</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TicketPriority</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Ticket priority</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>LOW, NORMAL, HIGH, URGENT</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>/tickets priority badges</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>AuditEvent</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Admin action log</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>adminId/email/role, action, entityType, entityId, summary, changes (Json), ip, userAgent, createdAt</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>/audit + CSV export</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise/fleet accounts</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>name, gstin, contact, cityId, walletBalance, status, reviewNote</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>/corporates</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>CorporateStatus</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Corporate KYC</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>PENDING, APPROVED, SUSPENDED</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>/corporates</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>CorporateMember</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Rider ↔ corporate mapping</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>corporateId, riderId (unique pair), employeeId, active</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>/corporates/[id] members tab</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>CorporateTopUp</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Wallet ledger entries</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>corporateId, amount (+/-), note, createdByAdminId, createdAt</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>/corporates/[id] wallet history</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -7957,12 +9066,12 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Support role already scoped in RBAC</t>
+          <t>Shipped — /tickets + /tickets/[id] with triage, priority, assignment, resolution</t>
         </is>
       </c>
     </row>
@@ -7992,12 +9101,12 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Post-MVP per SOW</t>
+          <t>Shipped — /audit with filters + CSV export + fraud signals; hooked into 9 mutating APIs</t>
         </is>
       </c>
     </row>
@@ -8027,12 +9136,12 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Post-MVP</t>
+          <t>Shipped — /corporates with members + wallet ledger; ride-fare deduction waits on payments</t>
         </is>
       </c>
     </row>

--- a/docs/Glimmora_Go_Spec.xlsx
+++ b/docs/Glimmora_Go_Spec.xlsx
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Everything: cities, fares, coupons, drivers, rides, reports, admins, partners, referrals</t>
+          <t>Everything in the admin panel — cities, fares, coupons, drivers, rides, tickets, reports, audit, partners, corporates, referrals, subscriptions, other admins</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Kirana Agent</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Admin Panel (full except admin user mgmt)</t>
+          <t>Kirana PWA</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>admin2@glimmora.ai / admin123</t>
+          <t>phone + 6-digit OTP</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Same as Super Admin minus the ability to create/delete admin users</t>
+          <t>Book rides on behalf of walk-in customers, view own bookings + commission, manage profile</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Global (all cities)</t>
+          <t>Own shop only (partnerId)</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
@@ -879,205 +879,30 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>City Admin</t>
+          <t>Trusted Contact / Ride Recipient</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Admin Panel (scoped)</t>
+          <t>Public Tracking Link</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>rewa.admin@glimmora.ai / admin123</t>
+          <t>no login (opaque token URL)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Driver approvals, local fare, ride monitoring, reports, partner approvals — only for assigned city</t>
+          <t>View one ride's live status + map. Used by riders' 'share-my-ride' and trusted-contact auto-SMS.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>One cityId from Admin.cityId</t>
+          <t>One ride only via trackingToken</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Verifier</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Admin Panel (drivers + docs only)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>verifier@glimmora.ai / admin123</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Approve/reject driver KYC documents. Sees only PENDING drivers. No access to other modules.</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>All cities, PENDING drivers only</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Support / QA</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Admin Panel (read + tickets write)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>support@glimmora.ai / admin123</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Monitor live rides, riders, reports, SOS; triage and resolve support tickets</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Read-only global; write on tickets</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Viewer</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Admin Panel (read-only)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>viewer@glimmora.ai / admin123</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Observer across all modules. Cannot write.</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Read-only global</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Kirana Agent</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Kirana PWA</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>phone + 6-digit OTP</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Book rides on behalf of walk-in customers, view own bookings + commission, manage profile</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Own shop only (partnerId)</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Trusted Contact / Ride Recipient</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Public Tracking Link</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>no login (opaque token URL)</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>View one ride's live status + map. Used by riders' 'share-my-ride' and trusted-contact auto-SMS.</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>One ride only via trackingToken</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1094,17 +919,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1115,35 +937,20 @@
       </c>
       <c r="B1" s="11" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Kirana Agent</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>City Admin</t>
+          <t>Trusted Contact</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>Verifier</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
-        <is>
-          <t>Viewer</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1162,30 +969,15 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>R (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Stats + recent rides</t>
         </is>
@@ -1204,30 +996,15 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Cancel/complete/reassign/share</t>
         </is>
@@ -1246,30 +1023,15 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>R (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Live sidebar badge</t>
         </is>
@@ -1288,30 +1050,15 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>R (PENDING only)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1326,30 +1073,15 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Per-document approve/reject + note</t>
         </is>
@@ -1368,30 +1100,15 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Search + lifetime spend</t>
         </is>
@@ -1410,30 +1127,15 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Per-city fare config</t>
         </is>
@@ -1452,7 +1154,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1461,21 +1163,6 @@
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Women/senior/children multipliers</t>
         </is>
@@ -1494,7 +1181,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1503,21 +1190,6 @@
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Flat/%, usage limit, expiry</t>
         </is>
@@ -1536,7 +1208,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1545,21 +1217,6 @@
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Includes archetype defaults editor</t>
         </is>
@@ -1578,7 +1235,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1587,21 +1244,6 @@
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Auto-reward + manual override</t>
         </is>
@@ -1610,91 +1252,61 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Subscriptions</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>R (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Includes CSV export + city breakdown</t>
+          <t>Grant/revoke driver plans</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Kirana Partners</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Approve/reject + commission</t>
+          <t>Includes CSV export + city breakdown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Admins</t>
+          <t>Kirana Partners</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1714,29 +1326,14 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Super Admin only</t>
+          <t>Approve/reject + commission</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Tickets</t>
+          <t>Admins</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1746,49 +1343,34 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>SUPPORT role can triage</t>
+          <t>Self-delete/deactivate still blocked</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Audit / Compliance</t>
+          <t>Tickets</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1798,113 +1380,68 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Read-only log; fraud signals panel</t>
+          <t>Create / triage / resolve</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Enterprise (B2B)</t>
+          <t>Audit / Compliance</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>W (own city)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Corporate accounts + wallet</t>
+          <t>Read-only log + fraud signals + CSV export</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Track public</t>
+          <t>Enterprise (B2B)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Public, opaque token</t>
+          <t>Corporate accounts + wallet ledger</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Kirana PWA</t>
+          <t>Kirana Book / History / Profile</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1914,32 +1451,44 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
+          <t>W (own shop)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Kirana agent PWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Track public</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Separate auth; agents only</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>R (one ride)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Public, opaque token link</t>
         </is>
       </c>
     </row>

--- a/docs/Glimmora_Go_Spec.xlsx
+++ b/docs/Glimmora_Go_Spec.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permissions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin Panel" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kirana PWA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partner PWA" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APIs" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gaps" sheetId="8" state="visible" r:id="rId8"/>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Frontend team: admin panel (Next.js) + Kirana PWA + public tracking</t>
+          <t>Frontend team: admin panel (Next.js) + Partner PWA + public tracking</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Kirana PWA</t>
+          <t>Partner PWA</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Kirana Agent</t>
+          <t>Partner Agent</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Kirana PWA</t>
+          <t>Partner PWA</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>Kirana Agent</t>
+          <t>Partner Agent</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Kirana Partners</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Kirana Book / History / Profile</t>
+          <t>Partner Book / History / Profile</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Kirana agent PWA</t>
+          <t>Partner PWA</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>KIRANA PARTNERS (admin side)</t>
+          <t>PARTNERS (admin side)</t>
         </is>
       </c>
       <c r="B60" s="14" t="n"/>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>/k/signup</t>
+          <t>/p/signup</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>/k/signup</t>
+          <t>/p/signup</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>'Application submitted' with link to /k/login</t>
+          <t>'Application submitted' with link to /p/login</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>/k/login</t>
+          <t>/p/login</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>10-digit validation, 'Send OTP' triggers /api/kirana/otp/request</t>
+          <t>10-digit validation, 'Send OTP' triggers /api/partner/otp/request</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>/k/login</t>
+          <t>/p/login</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>/k/login</t>
+          <t>/p/login</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/verify sets glimmora_kirana_session cookie</t>
+          <t>/api/partner/otp/verify sets glimmora_partner_session cookie</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>POST /api/kirana/logout clears cookie → redirect /k/login</t>
+          <t>POST /api/partner/logout clears cookie → redirect /p/login</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>/k</t>
+          <t>/p</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>/k</t>
+          <t>/p</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>/k</t>
+          <t>/p</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>'Book a ride for a customer' → /k/book</t>
+          <t>'Book a ride for a customer' → /p/book</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>/k</t>
+          <t>/p</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>PUT /api/kirana/bookings returns fare + distance + duration + your commission</t>
+          <t>PUT /api/partner/bookings returns fare + distance + duration + your commission</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>POST /api/kirana/bookings creates Ride with bookingChannel=KIRANA, bookedByPartnerId=self</t>
+          <t>POST /api/partner/bookings creates Ride with bookingChannel=KIRANA, bookedByPartnerId=self</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>/k/book</t>
+          <t>/p/book</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>/k/bookings</t>
+          <t>/p/bookings</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>/k/bookings</t>
+          <t>/p/bookings</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>/k/profile</t>
+          <t>/p/profile</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>/k/profile</t>
+          <t>/p/profile</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>/k/profile</t>
+          <t>/p/profile</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Pick type + file, upload to /api/kirana/documents; shows per-doc PENDING/APPROVED/REJECTED badge</t>
+          <t>Pick type + file, upload to /api/partner/documents; shows per-doc PENDING/APPROVED/REJECTED badge</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>all kirana routes</t>
+          <t>all partner routes</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Cache-first static, network-first kirana APIs, offline fallback to /offline.html</t>
+          <t>Cache-first static, network-first partner APIs, offline fallback to /offline.html</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>react-i18next across all kirana strings</t>
+          <t>react-i18next across all partner strings</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/signup</t>
+          <t>/api/partner/signup</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/request</t>
+          <t>/api/partner/otp/request</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/otp/verify</t>
+          <t>/api/partner/otp/verify</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Verify OTP + set kirana session cookie</t>
+          <t>Verify OTP + set partner session cookie</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/logout</t>
+          <t>/api/partner/logout</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Clear kirana session</t>
+          <t>Clear partner session</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>kirana session</t>
+          <t>partner session</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/bookings</t>
+          <t>/api/partner/bookings</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>kirana session (any status)</t>
+          <t>partner session (any status)</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>/api/kirana/bookings</t>
+          <t>/api/partner/bookings</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>kirana session (APPROVED only)</t>
+          <t>partner session (APPROVED only)</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>/riders, kirana signup auto-creates</t>
+          <t>/riders, partner signup auto-creates</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>/rides, /track, /sos, /reports, kirana bookings</t>
+          <t>/rides, /track, /sos, /reports, partner bookings</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Reports, kirana rides</t>
+          <t>Reports, partner rides</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -7517,12 +7517,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>KiranaPartner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Agent/kirana partners</t>
+          <t>Agent/partner partners</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>/partners, Kirana PWA</t>
+          <t>/partners, Partner PWA</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Kirana /k/profile upload + /partners/[id] review</t>
+          <t>Kirana /p/profile upload + /partners/[id] review</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>KIRANA_LOGIN, RIDER_LOGIN, DRIVER_LOGIN</t>
+          <t>PARTNER_LOGIN, RIDER_LOGIN, DRIVER_LOGIN</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Kirana PWA</t>
+          <t>Partner PWA</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Booking status push to kirana partners</t>
+          <t>Booking status push to partner partners</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Bookings detail + live track in Kirana PWA</t>
+          <t>Bookings detail + live track in Partner PWA</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Kirana PWA</t>
+          <t>Partner PWA</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
